--- a/수익시각화보고서.xlsx
+++ b/수익시각화보고서.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GalaxyBook3Pro\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GalaxyBook3Pro\Documents\Decision_Making_System_GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEA45B2-6046-4C56-91C5-CC5043C83D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6610EEC0-CFA7-493F-ADC7-253262AA29F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{F982AB9A-D822-46B7-8FEE-42C01CA840CE}"/>
   </bookViews>
@@ -190,7 +190,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -230,6 +230,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -833,7 +839,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1065,6 +1071,33 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1093,30 +1126,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1486,67 +1495,67 @@
       </c>
       <c r="G1" s="65">
         <f t="shared" si="0"/>
-        <v>-4968710</v>
+        <v>-15212710</v>
       </c>
       <c r="H1" s="66">
         <f t="shared" si="0"/>
-        <v>29661080</v>
+        <v>29267080</v>
       </c>
       <c r="I1" s="67">
         <f t="shared" si="0"/>
-        <v>-52732470</v>
+        <v>-53126470</v>
       </c>
       <c r="J1" s="65">
         <f t="shared" si="0"/>
-        <v>-2332470</v>
+        <v>-2726470</v>
       </c>
       <c r="K1" s="65">
         <f t="shared" si="0"/>
-        <v>-2332470</v>
+        <v>-2726470</v>
       </c>
       <c r="L1" s="65">
         <f t="shared" si="0"/>
-        <v>-2332470</v>
+        <v>-2726470</v>
       </c>
       <c r="M1" s="65">
         <f t="shared" si="0"/>
-        <v>-2332470</v>
+        <v>-2726470</v>
       </c>
       <c r="N1" s="65">
         <f t="shared" si="0"/>
-        <v>-2332470</v>
+        <v>-2726470</v>
       </c>
       <c r="O1" s="66">
         <f t="shared" si="0"/>
-        <v>-2332470</v>
+        <v>-2726470</v>
       </c>
       <c r="P1" s="67">
         <f t="shared" si="0"/>
-        <v>-2332470</v>
+        <v>-2726470</v>
       </c>
       <c r="Q1" s="65">
         <f t="shared" si="0"/>
-        <v>-2332470</v>
+        <v>-2726470</v>
       </c>
       <c r="R1" s="65">
         <f t="shared" si="0"/>
-        <v>-2332470</v>
+        <v>-2726470</v>
       </c>
       <c r="S1" s="65">
         <f t="shared" si="0"/>
-        <v>-2332470</v>
+        <v>-2726470</v>
       </c>
       <c r="T1" s="65">
         <f t="shared" si="0"/>
-        <v>-2332470</v>
+        <v>-2726470</v>
       </c>
       <c r="U1" s="65">
         <f t="shared" si="0"/>
-        <v>-2332470</v>
+        <v>-2726470</v>
       </c>
       <c r="V1" s="66">
         <f t="shared" si="0"/>
-        <v>-2332470</v>
+        <v>-2726470</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.6">
@@ -1664,67 +1673,67 @@
       </c>
       <c r="G3" s="72">
         <f t="shared" si="2"/>
-        <v>35066260</v>
+        <v>45310260</v>
       </c>
       <c r="H3" s="72">
         <f t="shared" si="2"/>
-        <v>436470</v>
+        <v>830470</v>
       </c>
       <c r="I3" s="71">
         <f t="shared" si="2"/>
-        <v>52732470</v>
+        <v>53126470</v>
       </c>
       <c r="J3" s="72">
         <f t="shared" si="2"/>
-        <v>2332470</v>
+        <v>2726470</v>
       </c>
       <c r="K3" s="72">
         <f t="shared" si="2"/>
-        <v>2332470</v>
+        <v>2726470</v>
       </c>
       <c r="L3" s="72">
         <f t="shared" si="2"/>
-        <v>2332470</v>
+        <v>2726470</v>
       </c>
       <c r="M3" s="72">
         <f t="shared" si="2"/>
-        <v>2332470</v>
+        <v>2726470</v>
       </c>
       <c r="N3" s="72">
         <f t="shared" si="2"/>
-        <v>2332470</v>
+        <v>2726470</v>
       </c>
       <c r="O3" s="72">
         <f t="shared" si="2"/>
-        <v>2332470</v>
+        <v>2726470</v>
       </c>
       <c r="P3" s="71">
         <f t="shared" si="2"/>
-        <v>2332470</v>
+        <v>2726470</v>
       </c>
       <c r="Q3" s="72">
         <f t="shared" si="2"/>
-        <v>2332470</v>
+        <v>2726470</v>
       </c>
       <c r="R3" s="72">
         <f t="shared" si="2"/>
-        <v>2332470</v>
+        <v>2726470</v>
       </c>
       <c r="S3" s="72">
         <f t="shared" si="2"/>
-        <v>2332470</v>
+        <v>2726470</v>
       </c>
       <c r="T3" s="72">
         <f t="shared" si="2"/>
-        <v>2332470</v>
+        <v>2726470</v>
       </c>
       <c r="U3" s="72">
         <f t="shared" si="2"/>
-        <v>2332470</v>
+        <v>2726470</v>
       </c>
       <c r="V3" s="73">
         <f>V71+V67+V62+V58+V55+V52+V51+V48+V47+V46+V45+V44</f>
-        <v>2332470</v>
+        <v>2726470</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65"/>
@@ -1964,12 +1973,6 @@
       <c r="U10" s="12"/>
       <c r="V10" s="13"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.6">
-      <c r="H11" s="1">
-        <f>AVERAGE(B20:H20)</f>
-        <v>471333.33333333331</v>
-      </c>
-    </row>
     <row r="12" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A12" s="1" t="s">
         <v>12</v>
@@ -2046,7 +2049,7 @@
       <c r="V14" s="13"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.6">
-      <c r="A15" s="84" t="s">
+      <c r="A15" s="93" t="s">
         <v>2</v>
       </c>
       <c r="B15" s="23" t="str">
@@ -2135,7 +2138,7 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.6">
-      <c r="A16" s="85"/>
+      <c r="A16" s="94"/>
       <c r="B16" s="2"/>
       <c r="D16" s="29">
         <v>754000</v>
@@ -2147,7 +2150,7 @@
       <c r="V16" s="18"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.6">
-      <c r="A17" s="85"/>
+      <c r="A17" s="94"/>
       <c r="B17" s="29">
         <f>52000-IF(B15="", 0, B15)+B16</f>
         <v>52000</v>
@@ -2234,7 +2237,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.6">
-      <c r="A18" s="85"/>
+      <c r="A18" s="94"/>
       <c r="B18" s="2" t="str">
         <f>IF(B17&lt;0, -B17, "")</f>
         <v/>
@@ -2321,7 +2324,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A19" s="85"/>
+      <c r="A19" s="94"/>
       <c r="B19" s="2" t="str">
         <f t="shared" ref="B19:H19" si="7">IF(E18="", "", E18)</f>
         <v/>
@@ -2874,7 +2877,7 @@
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.6">
-      <c r="A27" s="85" t="s">
+      <c r="A27" s="94" t="s">
         <v>4</v>
       </c>
       <c r="B27" s="2">
@@ -2963,10 +2966,10 @@
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.6">
-      <c r="A28" s="85"/>
+      <c r="A28" s="94"/>
       <c r="B28" s="2"/>
-      <c r="G28" s="1">
-        <v>121000</v>
+      <c r="G28" s="85">
+        <v>318000</v>
       </c>
       <c r="H28" s="18"/>
       <c r="I28" s="2"/>
@@ -2975,7 +2978,7 @@
       <c r="V28" s="18"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.6">
-      <c r="A29" s="85"/>
+      <c r="A29" s="94"/>
       <c r="B29" s="29">
         <f>487000-IF(B27="", 0, B27)+B28</f>
         <v>404000</v>
@@ -2997,221 +3000,221 @@
         <v>58000</v>
       </c>
       <c r="G29" s="1">
-        <f t="shared" ref="G29" si="23">F29-IF(G27="", 0, G27)+G28</f>
-        <v>0</v>
+        <f>F29-IF(G27="", 0, G27)+G28</f>
+        <v>197000</v>
       </c>
       <c r="H29" s="18">
-        <f t="shared" ref="H29" si="24">G29-IF(H27="", 0, H27)+H28</f>
-        <v>0</v>
+        <f t="shared" ref="H29" si="23">G29-IF(H27="", 0, H27)+H28</f>
+        <v>197000</v>
       </c>
       <c r="I29" s="2">
         <f>H29-IF(I27="", 0, I27)+I28</f>
-        <v>0</v>
+        <v>197000</v>
       </c>
       <c r="J29" s="1">
-        <f t="shared" ref="J29" si="25">I29-IF(J27="", 0, J27)+J28</f>
-        <v>0</v>
+        <f t="shared" ref="J29" si="24">I29-IF(J27="", 0, J27)+J28</f>
+        <v>197000</v>
       </c>
       <c r="K29" s="1">
-        <f t="shared" ref="K29" si="26">J29-IF(K27="", 0, K27)+K28</f>
-        <v>0</v>
+        <f t="shared" ref="K29" si="25">J29-IF(K27="", 0, K27)+K28</f>
+        <v>197000</v>
       </c>
       <c r="L29" s="1">
-        <f t="shared" ref="L29" si="27">K29-IF(L27="", 0, L27)+L28</f>
-        <v>0</v>
+        <f t="shared" ref="L29" si="26">K29-IF(L27="", 0, L27)+L28</f>
+        <v>197000</v>
       </c>
       <c r="M29" s="1">
-        <f t="shared" ref="M29" si="28">L29-IF(M27="", 0, M27)+M28</f>
-        <v>0</v>
+        <f t="shared" ref="M29" si="27">L29-IF(M27="", 0, M27)+M28</f>
+        <v>197000</v>
       </c>
       <c r="N29" s="1">
-        <f t="shared" ref="N29" si="29">M29-IF(N27="", 0, N27)+N28</f>
-        <v>0</v>
+        <f t="shared" ref="N29" si="28">M29-IF(N27="", 0, N27)+N28</f>
+        <v>197000</v>
       </c>
       <c r="O29" s="18">
-        <f t="shared" ref="O29" si="30">N29-IF(O27="", 0, O27)+O28</f>
-        <v>0</v>
+        <f t="shared" ref="O29" si="29">N29-IF(O27="", 0, O27)+O28</f>
+        <v>197000</v>
       </c>
       <c r="P29" s="2">
-        <f t="shared" ref="P29" si="31">O29-IF(P27="", 0, P27)+P28</f>
-        <v>0</v>
+        <f t="shared" ref="P29" si="30">O29-IF(P27="", 0, P27)+P28</f>
+        <v>197000</v>
       </c>
       <c r="Q29" s="1">
-        <f t="shared" ref="Q29" si="32">P29-IF(Q27="", 0, Q27)+Q28</f>
-        <v>0</v>
+        <f t="shared" ref="Q29" si="31">P29-IF(Q27="", 0, Q27)+Q28</f>
+        <v>197000</v>
       </c>
       <c r="R29" s="1">
-        <f t="shared" ref="R29" si="33">Q29-IF(R27="", 0, R27)+R28</f>
-        <v>0</v>
+        <f t="shared" ref="R29" si="32">Q29-IF(R27="", 0, R27)+R28</f>
+        <v>197000</v>
       </c>
       <c r="S29" s="1">
-        <f t="shared" ref="S29" si="34">R29-IF(S27="", 0, S27)+S28</f>
-        <v>0</v>
+        <f t="shared" ref="S29" si="33">R29-IF(S27="", 0, S27)+S28</f>
+        <v>197000</v>
       </c>
       <c r="T29" s="1">
-        <f t="shared" ref="T29" si="35">S29-IF(T27="", 0, T27)+T28</f>
-        <v>0</v>
+        <f t="shared" ref="T29" si="34">S29-IF(T27="", 0, T27)+T28</f>
+        <v>197000</v>
       </c>
       <c r="U29" s="1">
-        <f t="shared" ref="U29" si="36">T29-IF(U27="", 0, U27)+U28</f>
-        <v>0</v>
+        <f t="shared" ref="U29" si="35">T29-IF(U27="", 0, U27)+U28</f>
+        <v>197000</v>
       </c>
       <c r="V29" s="18">
-        <f t="shared" ref="V29" si="37">U29-IF(V27="", 0, V27)+V28</f>
-        <v>0</v>
+        <f t="shared" ref="V29" si="36">U29-IF(V27="", 0, V27)+V28</f>
+        <v>197000</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.6">
-      <c r="A30" s="85"/>
+      <c r="A30" s="94"/>
       <c r="B30" s="2" t="str">
-        <f t="shared" ref="B30:V30" si="38">IF(B29&lt;0, -B29, "")</f>
+        <f t="shared" ref="B30:V30" si="37">IF(B29&lt;0, -B29, "")</f>
         <v/>
       </c>
       <c r="C30" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="D30" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="F30" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="G30" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="H30" s="18" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="I30" s="2" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="J30" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="K30" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="L30" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="M30" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N30" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="O30" s="18" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P30" s="2" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="Q30" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="R30" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="S30" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="T30" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="U30" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V30" s="18" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A31" s="95"/>
+      <c r="B31" s="20" t="str">
+        <f t="shared" ref="B31:H31" si="38">IF(G30="", "", G30)</f>
+        <v/>
+      </c>
+      <c r="C31" s="19" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="D31" s="19" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="E30" s="1" t="str">
+      <c r="E31" s="19" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="F30" s="1" t="str">
+      <c r="F31" s="19" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="G30" s="1" t="str">
+      <c r="G31" s="19" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="H30" s="18" t="str">
+      <c r="H31" s="21" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="I30" s="2" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="J30" s="1" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="K30" s="1" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="L30" s="1" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="M30" s="1" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="N30" s="1" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="O30" s="18" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P30" s="2" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="Q30" s="1" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="R30" s="1" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="S30" s="1" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="T30" s="1" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="U30" s="1" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="V30" s="18" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A31" s="86"/>
-      <c r="B31" s="20" t="str">
-        <f t="shared" ref="B31:H31" si="39">IF(G30="", "", G30)</f>
-        <v/>
-      </c>
-      <c r="C31" s="19" t="str">
+      <c r="I31" s="20" t="str">
+        <f t="shared" ref="I31:Q31" si="39">IF(N30="", "", N30)</f>
+        <v/>
+      </c>
+      <c r="J31" s="19" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="D31" s="19" t="str">
+      <c r="K31" s="19" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="E31" s="19" t="str">
+      <c r="L31" s="19" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="F31" s="19" t="str">
+      <c r="M31" s="19" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="G31" s="19" t="str">
+      <c r="N31" s="19" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="H31" s="21" t="str">
+      <c r="O31" s="21" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="I31" s="20" t="str">
-        <f t="shared" ref="I31:Q31" si="40">IF(N30="", "", N30)</f>
-        <v/>
-      </c>
-      <c r="J31" s="19" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="K31" s="19" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="L31" s="19" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="M31" s="19" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="N31" s="19" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="O31" s="21" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
       <c r="P31" s="20" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Q31" s="19" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="R31" s="19" t="str">
@@ -3237,104 +3240,104 @@
     </row>
     <row r="33" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65"/>
     <row r="34" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A34" s="82" t="s">
+      <c r="A34" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="83"/>
+      <c r="B34" s="92"/>
     </row>
     <row r="35" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65"/>
     <row r="36" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B36" s="77" t="s">
+      <c r="B36" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="78"/>
+      <c r="C36" s="87"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.6">
       <c r="A37" s="50" t="s">
         <v>2</v>
       </c>
       <c r="B37" s="55">
-        <f t="shared" ref="B37:V37" si="41">B17</f>
+        <f t="shared" ref="B37:V37" si="40">B17</f>
         <v>52000</v>
       </c>
       <c r="C37" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>52000</v>
       </c>
       <c r="D37" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>552000</v>
       </c>
       <c r="E37" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>281000</v>
       </c>
       <c r="F37" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="G37" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="H37" s="35">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="I37" s="33">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="J37" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="K37" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="L37" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="M37" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="N37" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="O37" s="35">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="P37" s="33">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="Q37" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="R37" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="S37" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="T37" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U37" s="34">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="V37" s="35">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
@@ -3343,87 +3346,87 @@
         <v>3</v>
       </c>
       <c r="B38" s="38">
-        <f t="shared" ref="B38:V38" si="42">B23</f>
+        <f t="shared" ref="B38:V38" si="41">B23</f>
         <v>262000</v>
       </c>
       <c r="C38" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>88000</v>
       </c>
       <c r="D38" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1814000</v>
       </c>
       <c r="E38" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1092000</v>
       </c>
       <c r="F38" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>358000</v>
       </c>
       <c r="G38" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="H38" s="37">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="I38" s="36">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1896000</v>
       </c>
       <c r="J38" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1896000</v>
       </c>
       <c r="K38" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1896000</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1896000</v>
       </c>
       <c r="M38" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1896000</v>
       </c>
       <c r="N38" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1896000</v>
       </c>
       <c r="O38" s="37">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1896000</v>
       </c>
       <c r="P38" s="36">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1896000</v>
       </c>
       <c r="Q38" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1896000</v>
       </c>
       <c r="R38" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1896000</v>
       </c>
       <c r="S38" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1896000</v>
       </c>
       <c r="T38" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1896000</v>
       </c>
       <c r="U38" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1896000</v>
       </c>
       <c r="V38" s="37">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>1896000</v>
       </c>
     </row>
@@ -3432,88 +3435,88 @@
         <v>4</v>
       </c>
       <c r="B39" s="38">
-        <f t="shared" ref="B39:V39" si="43">B29</f>
+        <f t="shared" ref="B39:V39" si="42">B29</f>
         <v>404000</v>
       </c>
       <c r="C39" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>317000</v>
       </c>
       <c r="D39" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>234000</v>
       </c>
       <c r="E39" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>144000</v>
       </c>
       <c r="F39" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>58000</v>
       </c>
       <c r="G39" s="1">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>197000</v>
       </c>
       <c r="H39" s="37">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>197000</v>
       </c>
       <c r="I39" s="36">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>197000</v>
       </c>
       <c r="J39" s="1">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>197000</v>
       </c>
       <c r="K39" s="1">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>197000</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>197000</v>
       </c>
       <c r="M39" s="1">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>197000</v>
       </c>
       <c r="N39" s="1">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>197000</v>
       </c>
       <c r="O39" s="37">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>197000</v>
       </c>
       <c r="P39" s="36">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>197000</v>
       </c>
       <c r="Q39" s="1">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>197000</v>
       </c>
       <c r="R39" s="1">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>197000</v>
       </c>
       <c r="S39" s="1">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>197000</v>
       </c>
       <c r="T39" s="1">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>197000</v>
       </c>
       <c r="U39" s="1">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>197000</v>
       </c>
       <c r="V39" s="37">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>197000</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.6">
@@ -3529,79 +3532,79 @@
         <v>27500</v>
       </c>
       <c r="D40" s="1">
-        <f t="shared" ref="D40:V40" si="44">C40+D13-D6</f>
+        <f t="shared" ref="D40:V40" si="43">C40+D13-D6</f>
         <v>6500</v>
       </c>
       <c r="E40" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>2500</v>
       </c>
       <c r="F40" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
       <c r="G40" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
       <c r="H40" s="37">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
       <c r="I40" s="36">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
       <c r="J40" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
       <c r="K40" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
       <c r="M40" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
       <c r="N40" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
       <c r="O40" s="37">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
       <c r="P40" s="36">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
       <c r="Q40" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
       <c r="R40" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
       <c r="S40" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
       <c r="T40" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
       <c r="U40" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
       <c r="V40" s="37">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8500</v>
       </c>
     </row>
@@ -3618,175 +3621,175 @@
         <v>-1986</v>
       </c>
       <c r="D41" s="40">
-        <f t="shared" ref="D41:V41" si="45">C41+D14-D7</f>
+        <f t="shared" ref="D41:V41" si="44">C41+D14-D7</f>
         <v>-4979</v>
       </c>
       <c r="E41" s="40">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>-972</v>
       </c>
       <c r="F41" s="40">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>-965</v>
       </c>
       <c r="G41" s="40">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>92042</v>
       </c>
       <c r="H41" s="41">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>6049</v>
       </c>
       <c r="I41" s="39">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>6049</v>
       </c>
       <c r="J41" s="40">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>6049</v>
       </c>
       <c r="K41" s="40">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>6049</v>
       </c>
       <c r="L41" s="40">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>6049</v>
       </c>
       <c r="M41" s="40">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>6049</v>
       </c>
       <c r="N41" s="40">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>6049</v>
       </c>
       <c r="O41" s="41">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>6049</v>
       </c>
       <c r="P41" s="39">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>6049</v>
       </c>
       <c r="Q41" s="40">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>6049</v>
       </c>
       <c r="R41" s="40">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>6049</v>
       </c>
       <c r="S41" s="40">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>6049</v>
       </c>
       <c r="T41" s="40">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>6049</v>
       </c>
       <c r="U41" s="40">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>6049</v>
       </c>
       <c r="V41" s="41">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>6049</v>
       </c>
     </row>
     <row r="42" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65"/>
     <row r="43" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B43" s="77" t="s">
+      <c r="B43" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="78"/>
+      <c r="C43" s="87"/>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.6">
       <c r="A44" s="50" t="s">
         <v>2</v>
       </c>
       <c r="B44" s="33">
-        <f t="shared" ref="B44:V44" si="46">IF(B37&gt;0, B37*1, 0)</f>
+        <f t="shared" ref="B44:V44" si="45">IF(B37&gt;0, B37*1, 0)</f>
         <v>52000</v>
       </c>
       <c r="C44" s="34">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>52000</v>
       </c>
       <c r="D44" s="34">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>552000</v>
       </c>
       <c r="E44" s="34">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>281000</v>
       </c>
       <c r="F44" s="34">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="G44" s="34">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H44" s="35">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="I44" s="33">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="J44" s="34">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="K44" s="34">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L44" s="34">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="M44" s="34">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N44" s="34">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="O44" s="35">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="P44" s="33">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="Q44" s="34">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R44" s="34">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="S44" s="34">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="T44" s="34">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="U44" s="34">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="V44" s="35">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
     </row>
@@ -3799,83 +3802,83 @@
         <v>262000</v>
       </c>
       <c r="C45" s="1">
-        <f t="shared" ref="C45:V45" si="47">IF(C38&gt;0, C38*1, 0)</f>
+        <f t="shared" ref="C45:V45" si="46">IF(C38&gt;0, C38*1, 0)</f>
         <v>88000</v>
       </c>
       <c r="D45" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1814000</v>
       </c>
       <c r="E45" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1092000</v>
       </c>
       <c r="F45" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>358000</v>
       </c>
       <c r="G45" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="H45" s="37">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="I45" s="36">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1896000</v>
       </c>
       <c r="J45" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1896000</v>
       </c>
       <c r="K45" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1896000</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1896000</v>
       </c>
       <c r="M45" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1896000</v>
       </c>
       <c r="N45" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1896000</v>
       </c>
       <c r="O45" s="37">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1896000</v>
       </c>
       <c r="P45" s="36">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1896000</v>
       </c>
       <c r="Q45" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1896000</v>
       </c>
       <c r="R45" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1896000</v>
       </c>
       <c r="S45" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1896000</v>
       </c>
       <c r="T45" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1896000</v>
       </c>
       <c r="U45" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1896000</v>
       </c>
       <c r="V45" s="37">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>1896000</v>
       </c>
     </row>
@@ -3892,80 +3895,80 @@
         <v>634000</v>
       </c>
       <c r="D46" s="1">
-        <f t="shared" ref="D46:V46" si="48">IF(D39&gt;0, D39*2, 0)</f>
+        <f t="shared" ref="D46:V46" si="47">IF(D39&gt;0, D39*2, 0)</f>
         <v>468000</v>
       </c>
       <c r="E46" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>288000</v>
       </c>
       <c r="F46" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>116000</v>
       </c>
       <c r="G46" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="47"/>
+        <v>394000</v>
       </c>
       <c r="H46" s="37">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="47"/>
+        <v>394000</v>
       </c>
       <c r="I46" s="36">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="47"/>
+        <v>394000</v>
       </c>
       <c r="J46" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="47"/>
+        <v>394000</v>
       </c>
       <c r="K46" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="47"/>
+        <v>394000</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="47"/>
+        <v>394000</v>
       </c>
       <c r="M46" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="47"/>
+        <v>394000</v>
       </c>
       <c r="N46" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="47"/>
+        <v>394000</v>
       </c>
       <c r="O46" s="37">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="47"/>
+        <v>394000</v>
       </c>
       <c r="P46" s="36">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="47"/>
+        <v>394000</v>
       </c>
       <c r="Q46" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="47"/>
+        <v>394000</v>
       </c>
       <c r="R46" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="47"/>
+        <v>394000</v>
       </c>
       <c r="S46" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="47"/>
+        <v>394000</v>
       </c>
       <c r="T46" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="47"/>
+        <v>394000</v>
       </c>
       <c r="U46" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="47"/>
+        <v>394000</v>
       </c>
       <c r="V46" s="37">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="47"/>
+        <v>394000</v>
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.6">
@@ -3973,87 +3976,87 @@
         <v>0</v>
       </c>
       <c r="B47" s="36">
-        <f t="shared" ref="B47:V47" si="49">IF(B40&gt;0, B40*30, 0)</f>
+        <f t="shared" ref="B47:V47" si="48">IF(B40&gt;0, B40*30, 0)</f>
         <v>825000</v>
       </c>
       <c r="C47" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>825000</v>
       </c>
       <c r="D47" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>195000</v>
       </c>
       <c r="E47" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>75000</v>
       </c>
       <c r="F47" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
       <c r="G47" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
       <c r="H47" s="37">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
       <c r="I47" s="36">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
       <c r="J47" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
       <c r="K47" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
       <c r="M47" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
       <c r="N47" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
       <c r="O47" s="37">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
       <c r="P47" s="36">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
       <c r="Q47" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
       <c r="R47" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
       <c r="S47" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
       <c r="T47" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
       <c r="U47" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
       <c r="V47" s="37">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>255000</v>
       </c>
     </row>
@@ -4066,92 +4069,92 @@
         <v>0</v>
       </c>
       <c r="C48" s="40">
-        <f t="shared" ref="C48:V48" si="50">IF(C41&gt;0, C41*30, 0)</f>
+        <f t="shared" ref="C48:V48" si="49">IF(C41&gt;0, C41*30, 0)</f>
         <v>0</v>
       </c>
       <c r="D48" s="40">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="E48" s="40">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="F48" s="40">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="G48" s="40">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>2761260</v>
       </c>
       <c r="H48" s="41">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>181470</v>
       </c>
       <c r="I48" s="39">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>181470</v>
       </c>
       <c r="J48" s="40">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>181470</v>
       </c>
       <c r="K48" s="40">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>181470</v>
       </c>
       <c r="L48" s="40">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>181470</v>
       </c>
       <c r="M48" s="40">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>181470</v>
       </c>
       <c r="N48" s="40">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>181470</v>
       </c>
       <c r="O48" s="41">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>181470</v>
       </c>
       <c r="P48" s="39">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>181470</v>
       </c>
       <c r="Q48" s="40">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>181470</v>
       </c>
       <c r="R48" s="40">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>181470</v>
       </c>
       <c r="S48" s="40">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>181470</v>
       </c>
       <c r="T48" s="40">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>181470</v>
       </c>
       <c r="U48" s="40">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>181470</v>
       </c>
       <c r="V48" s="41">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>181470</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65"/>
     <row r="50" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B50" s="77" t="s">
+      <c r="B50" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="C50" s="78"/>
+      <c r="C50" s="87"/>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.6">
       <c r="A51" s="50" t="s">
@@ -4162,83 +4165,83 @@
         <v>0</v>
       </c>
       <c r="C51" s="34">
-        <f t="shared" ref="C51:V51" si="51">IF(C40&lt;0, -C40*250, 0)</f>
+        <f t="shared" ref="C51:V51" si="50">IF(C40&lt;0, -C40*250, 0)</f>
         <v>0</v>
       </c>
       <c r="D51" s="34">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="E51" s="34">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="F51" s="34">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="G51" s="34">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="H51" s="35">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I51" s="33">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="J51" s="34">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="K51" s="34">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="L51" s="34">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="M51" s="34">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="N51" s="34">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="O51" s="35">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="P51" s="33">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="Q51" s="34">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="R51" s="34">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="S51" s="34">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="T51" s="34">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="U51" s="34">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="V51" s="35">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
     </row>
@@ -4247,96 +4250,96 @@
         <v>1</v>
       </c>
       <c r="B52" s="39">
-        <f t="shared" ref="B52:V52" si="52">IF(B41&lt;0, -B41*250, 0)</f>
+        <f t="shared" ref="B52:V52" si="51">IF(B41&lt;0, -B41*250, 0)</f>
         <v>748250</v>
       </c>
       <c r="C52" s="40">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>496500</v>
       </c>
       <c r="D52" s="40">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>1244750</v>
       </c>
       <c r="E52" s="40">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>243000</v>
       </c>
       <c r="F52" s="40">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>241250</v>
       </c>
       <c r="G52" s="40">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="H52" s="41">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="I52" s="39">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J52" s="40">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="K52" s="40">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="L52" s="40">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M52" s="40">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="N52" s="40">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="O52" s="41">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="P52" s="39">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="Q52" s="40">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="R52" s="40">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="S52" s="40">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="T52" s="40">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="U52" s="40">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="V52" s="41">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65"/>
     <row r="54" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B54" s="77" t="s">
+      <c r="B54" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="C54" s="78"/>
+      <c r="C54" s="87"/>
     </row>
     <row r="55" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A55" s="50" t="s">
@@ -4347,83 +4350,83 @@
         <v>0</v>
       </c>
       <c r="C55" s="63">
-        <f t="shared" ref="C55:V55" si="53">C56+C57</f>
+        <f t="shared" ref="C55:V55" si="52">C56+C57</f>
         <v>0</v>
       </c>
       <c r="D55" s="63">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>23620000</v>
       </c>
       <c r="E55" s="63">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="F55" s="63">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="G55" s="63">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="H55" s="64">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="I55" s="49">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="J55" s="63">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K55" s="63">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="L55" s="63">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="M55" s="63">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="N55" s="63">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="O55" s="64">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="P55" s="49">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="Q55" s="63">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="R55" s="63">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="S55" s="63">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="T55" s="63">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="U55" s="63">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="V55" s="64">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
@@ -4432,87 +4435,87 @@
         <v>9</v>
       </c>
       <c r="B56" s="57">
-        <f t="shared" ref="B56:V56" si="54">IF(B16&gt;0, 1000000, 0)</f>
+        <f t="shared" ref="B56:V56" si="53">IF(B16&gt;0, 1000000, 0)</f>
         <v>0</v>
       </c>
       <c r="C56" s="58">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="D56" s="58">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>1000000</v>
       </c>
       <c r="E56" s="58">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="F56" s="58">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="G56" s="58">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="H56" s="59">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I56" s="57">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="J56" s="58">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="K56" s="58">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="L56" s="58">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="M56" s="58">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="N56" s="58">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="O56" s="59">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="P56" s="57">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="Q56" s="58">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="R56" s="58">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="S56" s="58">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="T56" s="58">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="U56" s="58">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="V56" s="59">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
     </row>
@@ -4521,87 +4524,87 @@
         <v>10</v>
       </c>
       <c r="B57" s="60">
-        <f t="shared" ref="B57:V57" si="55">B16*30</f>
+        <f t="shared" ref="B57:V57" si="54">B16*30</f>
         <v>0</v>
       </c>
       <c r="C57" s="61">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="D57" s="61">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>22620000</v>
       </c>
       <c r="E57" s="61">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="F57" s="61">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="G57" s="61">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="H57" s="62">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="I57" s="60">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="J57" s="61">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="K57" s="61">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L57" s="61">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M57" s="61">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="N57" s="61">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="O57" s="62">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="P57" s="60">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="Q57" s="61">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="R57" s="61">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="S57" s="61">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="T57" s="61">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="U57" s="61">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="V57" s="62">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
     </row>
@@ -4618,79 +4621,79 @@
         <v>0</v>
       </c>
       <c r="D58" s="63">
-        <f t="shared" ref="D58:J58" si="56">D59+D60+D61</f>
+        <f t="shared" ref="D58:J58" si="55">D59+D60+D61</f>
         <v>63000000</v>
       </c>
       <c r="E58" s="63">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="F58" s="63">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="G58" s="63">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="H58" s="63">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="I58" s="49">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>50400000</v>
       </c>
       <c r="J58" s="63">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="K58" s="63">
-        <f t="shared" ref="K58" si="57">K59+K60+K61</f>
+        <f t="shared" ref="K58" si="56">K59+K60+K61</f>
         <v>0</v>
       </c>
       <c r="L58" s="63">
-        <f t="shared" ref="L58" si="58">L59+L60+L61</f>
+        <f t="shared" ref="L58" si="57">L59+L60+L61</f>
         <v>0</v>
       </c>
       <c r="M58" s="63">
-        <f t="shared" ref="M58" si="59">M59+M60+M61</f>
+        <f t="shared" ref="M58" si="58">M59+M60+M61</f>
         <v>0</v>
       </c>
       <c r="N58" s="63">
-        <f t="shared" ref="N58" si="60">N59+N60+N61</f>
+        <f t="shared" ref="N58" si="59">N59+N60+N61</f>
         <v>0</v>
       </c>
       <c r="O58" s="63">
-        <f t="shared" ref="O58:Q58" si="61">O59+O60+O61</f>
+        <f t="shared" ref="O58:Q58" si="60">O59+O60+O61</f>
         <v>0</v>
       </c>
       <c r="P58" s="49">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="Q58" s="63">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="R58" s="63">
-        <f t="shared" ref="R58" si="62">R59+R60+R61</f>
+        <f t="shared" ref="R58" si="61">R59+R60+R61</f>
         <v>0</v>
       </c>
       <c r="S58" s="63">
-        <f t="shared" ref="S58" si="63">S59+S60+S61</f>
+        <f t="shared" ref="S58" si="62">S59+S60+S61</f>
         <v>0</v>
       </c>
       <c r="T58" s="63">
-        <f t="shared" ref="T58" si="64">T59+T60+T61</f>
+        <f t="shared" ref="T58" si="63">T59+T60+T61</f>
         <v>0</v>
       </c>
       <c r="U58" s="63">
-        <f t="shared" ref="U58" si="65">U59+U60+U61</f>
+        <f t="shared" ref="U58" si="64">U59+U60+U61</f>
         <v>0</v>
       </c>
       <c r="V58" s="64">
-        <f t="shared" ref="V58" si="66">V59+V60+V61</f>
+        <f t="shared" ref="V58" si="65">V59+V60+V61</f>
         <v>0</v>
       </c>
     </row>
@@ -4699,87 +4702,87 @@
         <v>9</v>
       </c>
       <c r="B59" s="57">
-        <f t="shared" ref="B59:V59" si="67">IF(B21&gt;0, 3000000, 0)</f>
+        <f t="shared" ref="B59:V59" si="66">IF(B21&gt;0, 3000000, 0)</f>
         <v>0</v>
       </c>
       <c r="C59" s="58">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="D59" s="58">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>3000000</v>
       </c>
       <c r="E59" s="58">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="F59" s="58">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="G59" s="58">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="H59" s="59">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="I59" s="57">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>3000000</v>
       </c>
       <c r="J59" s="58">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="K59" s="58">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="L59" s="58">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="M59" s="58">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="N59" s="58">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O59" s="59">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="P59" s="57">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="Q59" s="58">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="R59" s="58">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="S59" s="58">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="T59" s="58">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="U59" s="58">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="V59" s="59">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
     </row>
@@ -4788,87 +4791,87 @@
         <v>21</v>
       </c>
       <c r="B60" s="57">
-        <f t="shared" ref="B60:V60" si="68">B21*25</f>
+        <f t="shared" ref="B60:V60" si="67">B21*25</f>
         <v>0</v>
       </c>
       <c r="C60" s="58">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="D60" s="58">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>60000000</v>
       </c>
       <c r="E60" s="58">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="F60" s="58">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="G60" s="58">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="H60" s="59">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="I60" s="57">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>47400000</v>
       </c>
       <c r="J60" s="58">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K60" s="58">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="L60" s="58">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="M60" s="58">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="N60" s="58">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="O60" s="59">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="P60" s="57">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="Q60" s="58">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="R60" s="58">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="S60" s="58">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="T60" s="58">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="U60" s="58">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="V60" s="59">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
     </row>
@@ -4893,71 +4896,71 @@
         <v>0</v>
       </c>
       <c r="F61" s="61">
-        <f t="shared" ref="F61:V61" si="69">F22*50</f>
+        <f t="shared" ref="F61:V61" si="68">F22*50</f>
         <v>0</v>
       </c>
       <c r="G61" s="61">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="H61" s="62">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="I61" s="60">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="J61" s="61">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K61" s="61">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="L61" s="61">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M61" s="61">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="N61" s="61">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="O61" s="62">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="P61" s="60">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="Q61" s="61">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="R61" s="61">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="S61" s="61">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="T61" s="61">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="U61" s="61">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="V61" s="62">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
     </row>
@@ -4970,270 +4973,270 @@
         <v>0</v>
       </c>
       <c r="C62" s="34">
-        <f t="shared" ref="C62:V62" si="70">C63+C64</f>
+        <f t="shared" ref="C62:V62" si="69">C63+C64</f>
         <v>0</v>
       </c>
       <c r="D62" s="34">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="E62" s="34">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="F62" s="34">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="G62" s="34">
+        <f t="shared" si="69"/>
+        <v>17900000</v>
+      </c>
+      <c r="H62" s="35">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="I62" s="33">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="34">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="K62" s="34">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="L62" s="34">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="M62" s="34">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="N62" s="34">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="O62" s="35">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="P62" s="33">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="Q62" s="34">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="R62" s="34">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="S62" s="34">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="T62" s="34">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="U62" s="34">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="V62" s="35">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.6">
+      <c r="A63" s="77" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63" s="79">
+        <f>IF(B28&gt;0, 2000000, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="C63" s="80">
+        <f>IF(C28&gt;0, 2000000, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D63" s="80">
+        <f t="shared" ref="D63:V63" si="70">IF(D28&gt;0, 2000000, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="E63" s="80">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="E62" s="34">
+      <c r="F63" s="80">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="F62" s="34">
+      <c r="G63" s="80">
+        <f>IF(G28&gt;0, 2000000, 0)</f>
+        <v>2000000</v>
+      </c>
+      <c r="H63" s="81">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="G62" s="34">
+      <c r="I63" s="79">
         <f t="shared" si="70"/>
-        <v>8050000</v>
-      </c>
-      <c r="H62" s="35">
+        <v>0</v>
+      </c>
+      <c r="J63" s="80">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="I62" s="33">
+      <c r="K63" s="80">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="J62" s="34">
+      <c r="L63" s="80">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="K62" s="34">
+      <c r="M63" s="80">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="L62" s="34">
+      <c r="N63" s="80">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="M62" s="34">
+      <c r="O63" s="81">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="N62" s="34">
+      <c r="P63" s="79">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="O62" s="35">
+      <c r="Q63" s="80">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="P62" s="33">
+      <c r="R63" s="80">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="Q62" s="34">
+      <c r="S63" s="80">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="R62" s="34">
+      <c r="T63" s="80">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="S62" s="34">
+      <c r="U63" s="80">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="T62" s="34">
+      <c r="V63" s="81">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="U62" s="34">
-        <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="V62" s="35">
-        <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.6">
-      <c r="A63" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="B63" s="89">
-        <f>IF(B28&gt;0, 2000000, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="C63" s="90">
-        <f>IF(C28&gt;0, 2000000, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D63" s="90">
-        <f t="shared" ref="D63:V63" si="71">IF(D28&gt;0, 2000000, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="E63" s="90">
+    </row>
+    <row r="64" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A64" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="B64" s="82">
+        <f>B28*50</f>
+        <v>0</v>
+      </c>
+      <c r="C64" s="83">
+        <f t="shared" ref="C64:V64" si="71">C28*50</f>
+        <v>0</v>
+      </c>
+      <c r="D64" s="83">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="F63" s="90">
+      <c r="E64" s="83">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="G63" s="90">
+      <c r="F64" s="83">
         <f t="shared" si="71"/>
-        <v>2000000</v>
-      </c>
-      <c r="H63" s="91">
+        <v>0</v>
+      </c>
+      <c r="G64" s="83">
+        <f>G28*50</f>
+        <v>15900000</v>
+      </c>
+      <c r="H64" s="84">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="I63" s="89">
+      <c r="I64" s="82">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="J63" s="90">
+      <c r="J64" s="83">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="K63" s="90">
+      <c r="K64" s="83">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="L63" s="90">
+      <c r="L64" s="83">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="M63" s="90">
+      <c r="M64" s="83">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="N63" s="90">
+      <c r="N64" s="83">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="O63" s="91">
+      <c r="O64" s="84">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="P63" s="89">
+      <c r="P64" s="82">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="Q63" s="90">
+      <c r="Q64" s="83">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="R63" s="90">
+      <c r="R64" s="83">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="S63" s="90">
+      <c r="S64" s="83">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="T63" s="90">
+      <c r="T64" s="83">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="U63" s="90">
+      <c r="U64" s="83">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="V63" s="91">
+      <c r="V64" s="84">
         <f t="shared" si="71"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A64" s="88" t="s">
-        <v>10</v>
-      </c>
-      <c r="B64" s="92">
-        <f>B28*50</f>
-        <v>0</v>
-      </c>
-      <c r="C64" s="93">
-        <f t="shared" ref="C64:V64" si="72">C28*50</f>
-        <v>0</v>
-      </c>
-      <c r="D64" s="93">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="E64" s="93">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="F64" s="93">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="G64" s="93">
-        <f t="shared" si="72"/>
-        <v>6050000</v>
-      </c>
-      <c r="H64" s="94">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="I64" s="92">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="J64" s="93">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="K64" s="93">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="L64" s="93">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="M64" s="93">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="N64" s="93">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="O64" s="94">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="P64" s="92">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="Q64" s="93">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="R64" s="93">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="S64" s="93">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="T64" s="93">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="U64" s="93">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="V64" s="94">
-        <f t="shared" si="72"/>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65"/>
     <row r="66" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B66" s="79" t="s">
+      <c r="B66" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="C66" s="78"/>
+      <c r="C66" s="87"/>
     </row>
     <row r="67" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A67" s="50" t="s">
@@ -5244,83 +5247,83 @@
         <v>0</v>
       </c>
       <c r="C67" s="63">
-        <f t="shared" ref="C67:V67" si="73">SUM(C68:C70)</f>
+        <f t="shared" ref="C67:V67" si="72">SUM(C68:C70)</f>
         <v>0</v>
       </c>
       <c r="D67" s="63">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>26800000</v>
       </c>
       <c r="E67" s="63">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>28600000</v>
       </c>
       <c r="F67" s="63">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>27800000</v>
       </c>
       <c r="G67" s="63">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="H67" s="64">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="I67" s="49">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="J67" s="63">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K67" s="63">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="L67" s="63">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="M67" s="63">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="N67" s="63">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="O67" s="64">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="P67" s="49">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="Q67" s="63">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="R67" s="63">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="S67" s="63">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="T67" s="63">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="U67" s="63">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="V67" s="64">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
     </row>
@@ -5329,11 +5332,11 @@
         <v>6</v>
       </c>
       <c r="B68" s="57">
-        <f t="shared" ref="B68:V68" si="74">IF(B9&gt;0, 5000000, 0)</f>
+        <f t="shared" ref="B68:V68" si="73">IF(B9&gt;0, 5000000, 0)</f>
         <v>0</v>
       </c>
       <c r="C68" s="58">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="D68" s="58">
@@ -5341,75 +5344,75 @@
         <v>5000000</v>
       </c>
       <c r="E68" s="58">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>5000000</v>
       </c>
       <c r="F68" s="58">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>5000000</v>
       </c>
       <c r="G68" s="58">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="H68" s="59">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="I68" s="57">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="J68" s="58">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="K68" s="58">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="L68" s="58">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M68" s="58">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="N68" s="58">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="O68" s="59">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="P68" s="57">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="Q68" s="58">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="R68" s="58">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="S68" s="58">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="T68" s="58">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="U68" s="58">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="V68" s="59">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
     </row>
@@ -5418,87 +5421,87 @@
         <v>7</v>
       </c>
       <c r="B69" s="57">
-        <f t="shared" ref="B69:V69" si="75">QUOTIENT(B9,100) * 100000</f>
+        <f t="shared" ref="B69:V69" si="74">QUOTIENT(B9,100) * 100000</f>
         <v>0</v>
       </c>
       <c r="C69" s="58">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="D69" s="58">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>14400000</v>
       </c>
       <c r="E69" s="58">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>15300000</v>
       </c>
       <c r="F69" s="58">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>14900000</v>
       </c>
       <c r="G69" s="58">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="H69" s="59">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="I69" s="57">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="J69" s="58">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="K69" s="58">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="L69" s="58">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="M69" s="58">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="N69" s="58">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="O69" s="59">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="P69" s="57">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="Q69" s="58">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="R69" s="58">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="S69" s="58">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="T69" s="58">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="U69" s="58">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="V69" s="59">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
     </row>
@@ -5507,87 +5510,87 @@
         <v>8</v>
       </c>
       <c r="B70" s="60">
-        <f t="shared" ref="B70:V70" si="76">MAX(0, QUOTIENT(B9-7000,100)) * 100000</f>
+        <f t="shared" ref="B70:V70" si="75">MAX(0, QUOTIENT(B9-7000,100)) * 100000</f>
         <v>0</v>
       </c>
       <c r="C70" s="61">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="D70" s="61">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>7400000</v>
       </c>
       <c r="E70" s="61">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>8300000</v>
       </c>
       <c r="F70" s="61">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>7900000</v>
       </c>
       <c r="G70" s="61">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="H70" s="62">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="I70" s="60">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="J70" s="61">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="K70" s="61">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="L70" s="61">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="M70" s="61">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="N70" s="61">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="O70" s="62">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="P70" s="60">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="Q70" s="61">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="R70" s="61">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="S70" s="61">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="T70" s="61">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="U70" s="61">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="V70" s="62">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
     </row>
@@ -5600,83 +5603,83 @@
         <v>22600000</v>
       </c>
       <c r="C71" s="63">
-        <f t="shared" ref="C71:V71" si="77">SUM(C72:C74)</f>
+        <f t="shared" ref="C71:V71" si="76">SUM(C72:C74)</f>
         <v>19400000</v>
       </c>
       <c r="D71" s="63">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>17400000</v>
       </c>
       <c r="E71" s="63">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>15800000</v>
       </c>
       <c r="F71" s="63">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>12000000</v>
       </c>
       <c r="G71" s="63">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>24000000</v>
       </c>
       <c r="H71" s="64">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="I71" s="49">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="J71" s="63">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="K71" s="63">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="L71" s="63">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="M71" s="63">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N71" s="63">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="O71" s="64">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="P71" s="49">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="Q71" s="63">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="R71" s="63">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="S71" s="63">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="T71" s="63">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="U71" s="63">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="V71" s="64">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
     </row>
@@ -5685,11 +5688,11 @@
         <v>6</v>
       </c>
       <c r="B72" s="57">
-        <f t="shared" ref="B72:V72" si="78">IF(B10&gt;0, 4000000, 0)</f>
+        <f t="shared" ref="B72:V72" si="77">IF(B10&gt;0, 4000000, 0)</f>
         <v>4000000</v>
       </c>
       <c r="C72" s="58">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>4000000</v>
       </c>
       <c r="D72" s="58">
@@ -5697,75 +5700,75 @@
         <v>4000000</v>
       </c>
       <c r="E72" s="58">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>4000000</v>
       </c>
       <c r="F72" s="58">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>4000000</v>
       </c>
       <c r="G72" s="58">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>4000000</v>
       </c>
       <c r="H72" s="59">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="I72" s="57">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="J72" s="58">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="K72" s="58">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="L72" s="58">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="M72" s="58">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="N72" s="58">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="O72" s="59">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="P72" s="57">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="Q72" s="58">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="R72" s="58">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="S72" s="58">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="T72" s="58">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="U72" s="58">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="V72" s="59">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
     </row>
@@ -5774,87 +5777,87 @@
         <v>7</v>
       </c>
       <c r="B73" s="57">
-        <f t="shared" ref="B73:V73" si="79">QUOTIENT(B10,100) * 100000</f>
+        <f t="shared" ref="B73:V73" si="78">QUOTIENT(B10,100) * 100000</f>
         <v>12800000</v>
       </c>
       <c r="C73" s="58">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>11200000</v>
       </c>
       <c r="D73" s="58">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>10200000</v>
       </c>
       <c r="E73" s="58">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>9400000</v>
       </c>
       <c r="F73" s="58">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>7500000</v>
       </c>
       <c r="G73" s="58">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>13500000</v>
       </c>
       <c r="H73" s="59">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="I73" s="57">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="J73" s="58">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K73" s="58">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="L73" s="58">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="M73" s="58">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="N73" s="58">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="O73" s="59">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P73" s="57">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="Q73" s="58">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="R73" s="58">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="S73" s="58">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="T73" s="58">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="U73" s="58">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="V73" s="59">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
     </row>
@@ -5863,96 +5866,96 @@
         <v>8</v>
       </c>
       <c r="B74" s="60">
-        <f t="shared" ref="B74:V74" si="80">MAX(0, QUOTIENT(B10-7000,100)) * 100000</f>
+        <f t="shared" ref="B74:V74" si="79">MAX(0, QUOTIENT(B10-7000,100)) * 100000</f>
         <v>5800000</v>
       </c>
       <c r="C74" s="61">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>4200000</v>
       </c>
       <c r="D74" s="61">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>3200000</v>
       </c>
       <c r="E74" s="61">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>2400000</v>
       </c>
       <c r="F74" s="61">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>500000</v>
       </c>
       <c r="G74" s="61">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>6500000</v>
       </c>
       <c r="H74" s="62">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="I74" s="60">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="J74" s="61">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="K74" s="61">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="L74" s="61">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M74" s="61">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="N74" s="61">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="O74" s="62">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="P74" s="60">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q74" s="61">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="R74" s="61">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="S74" s="61">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="T74" s="61">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="U74" s="61">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="V74" s="62">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65"/>
     <row r="77" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A77" s="80" t="s">
+      <c r="A77" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="B77" s="81"/>
+      <c r="B77" s="90"/>
     </row>
     <row r="78" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.65"/>
     <row r="79" spans="1:22" x14ac:dyDescent="0.6">
@@ -5964,83 +5967,83 @@
         <v>0</v>
       </c>
       <c r="C79" s="34">
-        <f t="shared" ref="C79:V79" si="81">250*C6</f>
+        <f t="shared" ref="C79:V79" si="80">250*C6</f>
         <v>0</v>
       </c>
       <c r="D79" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>68750000</v>
       </c>
       <c r="E79" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>68750000</v>
       </c>
       <c r="F79" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>68750000</v>
       </c>
       <c r="G79" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="H79" s="35">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="I79" s="33">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="J79" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="K79" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L79" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="M79" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="N79" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="O79" s="35">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="P79" s="33">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="Q79" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="R79" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="S79" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="T79" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="U79" s="34">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="V79" s="35">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
     </row>
@@ -6053,83 +6056,83 @@
         <v>30097550</v>
       </c>
       <c r="C80" s="40">
-        <f t="shared" ref="C80:V80" si="82">350*C7</f>
+        <f t="shared" ref="C80:V80" si="81">350*C7</f>
         <v>30097550</v>
       </c>
       <c r="D80" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>30097550</v>
       </c>
       <c r="E80" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>30097550</v>
       </c>
       <c r="F80" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>30097550</v>
       </c>
       <c r="G80" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>30097550</v>
       </c>
       <c r="H80" s="41">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>30097550</v>
       </c>
       <c r="I80" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="J80" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="K80" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="L80" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="M80" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="N80" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="O80" s="41">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="P80" s="39">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="Q80" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="R80" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="S80" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="T80" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="U80" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="V80" s="41">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
     </row>
